--- a/Codelist Excel Files and Conversion Templates to XML/loadEfficacyDefinition.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/loadEfficacyDefinition.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Codes for which competing definition a diggs:RILTPDesignType/diggs:loadEfficacy value uses - load efficacy is defined at least three different ways in the literature, so a value reported without this code is not comparable across designs. Used for the value of diggs:RILTPDesignType/diggs:loadEfficacyDefinition.</t>
+          <t>Codes for which competing definition a diggs:DesignRILTPType/diggs:loadEfficacy value uses - load efficacy is defined at least three different ways in the literature, so a value reported without this code is not comparable across designs. Used for the value of diggs:DesignRILTPType/diggs:loadEfficacyDefinition.</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>//diggs:RILTPDesign/diggs:loadEfficacyDefinition</t>
+          <t>//diggs:DesignRILTP/diggs:loadEfficacyDefinition</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>//diggs:RILTPDesign/diggs:loadEfficacyDefinition</t>
+          <t>//diggs:DesignRILTP/diggs:loadEfficacyDefinition</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>//diggs:RILTPDesign/diggs:loadEfficacyDefinition</t>
+          <t>//diggs:DesignRILTP/diggs:loadEfficacyDefinition</t>
         </is>
       </c>
     </row>
